--- a/diseases/d122/2010-2014.xlsx
+++ b/diseases/d122/2010-2014.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D122</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Trichinellosis</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>旋毛虫病</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2013-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.01917808219178082</v>
-      </c>
       <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>foph_idd</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Switzerland FOPH IDD</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>foph_idd</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Switzerland FOPH IDD</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -690,46 +864,48 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>D122</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Trichinellosis</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>旋毛虫病</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -737,52 +913,871 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Tríkínusýking</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>foph_idd</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Switzerland FOPH IDD</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>foph_idd</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Switzerland FOPH IDD</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Tríkínusýking</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -898,62 +1893,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2014-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2014-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2010-01-01</t>
         </is>

--- a/diseases/d122/2010-2014.xlsx
+++ b/diseases/d122/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1455,9 +1452,6 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">

--- a/diseases/d122/2010-2014.xlsx
+++ b/diseases/d122/2010-2014.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,93 +751,104 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.01235910313449102</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -864,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,12 +910,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -913,17 +924,34 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -931,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -948,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -961,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1109,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1058,48 +1144,31 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.003138053468885109</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Tríkínusýking</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1107,64 +1176,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>1</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1182,7 +1193,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1195,42 +1206,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1268,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,93 +1303,179 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1507,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1440,12 +1537,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1464,7 +1561,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1489,7 +1586,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -1502,42 +1599,42 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1666,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1599,12 +1696,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1615,22 +1712,22 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Tríkínusýking</t>
+          <t>Trichinellosis</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1640,7 +1737,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1655,7 +1752,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1680,7 +1777,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1690,12 +1787,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1723,7 +1820,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1736,40 +1833,1908 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.01235910313449102</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
           <t>is_doh_annual</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Tríkínusýking</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Tríkínusýking</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TRICHINELLOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
@@ -1820,7 +3785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2010-01-01</t>
         </is>
       </c>
     </row>
@@ -1891,7 +3856,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1901,7 +3866,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -1921,7 +3886,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1931,7 +3896,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1953,7 +3918,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
